--- a/output/(山本)理解容易性_関係性_再構成.xlsx
+++ b/output/(山本)理解容易性_関係性_再構成.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26.13" customWidth="1" min="1" max="1"/>
@@ -461,14 +461,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>外部文書、リポジトリ、または文書内の他セクションを引用・参照する際、文書名、章節番号、図表番号、または一意のURL・パスを明記し、参照先の内容を遅滞なく特定できる状態にしている。</t>
+          <t>他の文書や仕様を根拠として記述を展開する際、読者が情報源へ迷わず到達できるよう、対象となる文書名、章番号、および固有の識別子（要求IDなど）を明記している。</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】先行研究の結果に基づき、本システムのアーキテクチャを決定した。（出典が不明であり、根拠の妥当性を確認できない）
-→【適合例】先行研究（［引用番号］：2023年度XX技術報告書）の結果に基づき、本システムのアーキテクチャを決定した。</t>
+【非適合例】基本設計書の機能F1の必要性については、要求仕様書を参照すること。（引用元となる文書の具体的な識別子が明示されておらず、追跡が困難である。）
+→【適合例】［例文1］基本設計書の機能F1の必要性については、関連する要求仕様書の「第3章（要求ID:R1およびR2）」を参照すること。</t>
         </is>
       </c>
     </row>
@@ -480,14 +480,14 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>文書の改訂において、旧版との具体的な相違点や変更箇所を、改訂履歴、比較表、または差分マーカーを用いて、変更の経緯と影響範囲が追跡可能な状態で記述している。</t>
+          <t>既存文書の更新や別版との比較を記述する際、対象となる元文書を特定するための属性情報（文書名、版番号など）と、具体的な変更箇所の章節番号をセットで明記している。</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】最新の仕様に合わせて本章の内容を全面的に更新した。（具体的な変更点や旧版との差異が不明）
-→【適合例】前バージョン（v1.2）からの変更点として、認証エラー時のリトライ回数を3回から5回に変更した。</t>
+【非適合例】前バージョンからの変更点を反映し、仕様を更新した。（元文書を特定する情報や具体的な修正箇所の提示がなく、変更による影響範囲を特定できない。）
+→【適合例】版番号1.1からの相違点として、第3章の認証API（セクション3.2.1）のタイムアウト値を30秒から60秒へ変更した。</t>
         </is>
       </c>
     </row>
@@ -499,71 +499,33 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>文書内の修正内容を一意に特定し検証するために、対象となる文書名、管理番号、版番号、更新日、および作成者をメタデータとして正確に記述している。</t>
+          <t>本文中で分散して解説した複数の構成要素を図表に集約して提示する際、対象となる要素群の固有名称や識別子を本文内で網羅的に列挙し、集約先となる図表番号を明記している。</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】不具合修正のため、基本設計書の一部を修正した。（修正対象の版や作成者が特定できない）
-→【適合例】基本設計書（文書番号：BD-001、版：v2.0、作成日：2024/03/25、作成者：山田）の第3章を、不具合報告書#123に基づき修正した。</t>
+【非適合例】センサDを10msec周期で入力する。各センサの入力周期は表3にまとめる。（対象となるセンサの全体像や個別の名称が明示されておらず、図表との対応関係が不明確である。）
+→【適合例】［例文2］センサDを10msec周期で入力する。以上に述べたセンサA、センサB、センサC、およびセンサDの入力周期の仕様については、表3にまとめる。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>関連する複数箇所の記述に対して、参照情報を明示している</t>
+          <t>記述内容は追跡可能である</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>特定の機能や仕様の決定根拠が他文書（要求定義書、標準規約、議事録等）に依存する場合、参照すべき具体的な文書名と節番号、または管理IDを付記し、根拠の連鎖を明示している。</t>
+          <t>仕様変更時の波及範囲を確実かつ迅速に特定できるよう、上位工程の要求事項と下位工程の設計要素（モジュールや関数など）との対応関係を、トレーサビリティマトリクスまたは一意のIDを用いて双方向に紐付けている。</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】基本設計書の機能F1の必要性を理解するには、要求仕様書を確認する必要がある。（具体的な要求IDが不明）
-→【適合例】基本設計書の機能F1の必要性を理解するには、関連する要求仕様書のR1およびR2を参照する必要がある。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>関連する複数箇所の記述に対して、参照情報を明示している</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>文書内で散在する情報を要約・集約して提示する場合、情報の重複や矛盾を防ぐため、出典元となる記述箇所（表番号、図番号、節番号等）との対応関係を明示している。</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>★新規追加
-【非適合例】各センサの入力周期は、前述した通りである。（どの節や表の記述を指しているか不明）
-→【適合例】各センサ（A、B、C、D）の入力周期を、第2.1節の各仕様に基づき表3に集約する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>記述内容は追跡可能である</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>上流工程の要件（要求ID等）と下流工程の設計・実装・テスト要素（機能ID、ソースコード、テストケース等）の対応関係を、トレーサビリティマトリクス等によって双方向に特定できる状態で記述している。</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>★新規追加
-【非適合例】基本設計書と詳細設計書の間で機能の対応関係が管理されていない。（設計変更時の影響範囲の追跡が困難）
-→【適合例】要求仕様書の要求R1を修正する際に、対応する基本設計書の機能F1および詳細設計書の機能詳細FS1を即座に特定できるよう、トレーサビリティマトリクスで紐付けを管理している。</t>
+【非適合例】要求R1の変更時は、関連する各設計書の該当箇所を修正すること。（具体的な要素間のリンクがなく、追跡対象を特定できない。）
+→【適合例】要求R1を変更する際は、トレーサビリティマトリクス（別紙A）を参照し、紐付けられた基本設計書の機能F1および詳細設計書の機能詳細FS1を修正すること。</t>
         </is>
       </c>
     </row>
